--- a/sheets/대금율보/검수/바램.xlsx
+++ b/sheets/대금율보/검수/바램.xlsx
@@ -7193,7 +7193,7 @@
       <c r="Q4" s="23"/>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹‹
+          <t xml:space="preserve">浹
 –汰</t>
         </is>
       </c>
@@ -7650,7 +7650,7 @@
       <c r="I10" s="27"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹‹
+          <t xml:space="preserve">浹
 –汰</t>
         </is>
       </c>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="T10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -7776,7 +7776,7 @@
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="O11" s="22" t="inlineStr">
@@ -7807,7 +7807,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕‹
+          <t xml:space="preserve">潕
 –湳</t>
         </is>
       </c>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 –無</t>
         </is>
       </c>
@@ -7843,7 +7843,7 @@
       <c r="K12" s="23"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋淋</t>
         </is>
       </c>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 –無</t>
         </is>
       </c>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –仲</t>
         </is>
       </c>
@@ -8216,7 +8216,7 @@
       <c r="O16" s="23"/>
       <c r="P16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –仲</t>
         </is>
       </c>
@@ -8311,7 +8311,7 @@
       <c r="C18" s="26"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –潢</t>
         </is>
       </c>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="N18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –南</t>
         </is>
       </c>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="P19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –潢</t>
         </is>
       </c>
@@ -8528,7 +8528,7 @@
       <c r="E20" s="23"/>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -8540,7 +8540,7 @@
       <c r="H20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕湳
-–潕‹</t>
+–潕</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -8574,7 +8574,7 @@
       <c r="O20" s="23"/>
       <c r="P20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -8687,7 +8687,7 @@
       <c r="E22" s="26"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/바램.xlsx
+++ b/sheets/대금율보/검수/바램.xlsx
@@ -7002,32 +7002,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.8" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.8" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.8" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.8" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="U6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.8" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.8" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.8" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.8" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.8" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.8" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.8" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.8" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="U14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.8" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.8" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -8230,7 +8230,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.8" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.8" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="91.8" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="91.8" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="24" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
       <c r="T20" s="21"/>
       <c r="U20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="91.8" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="24" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="91.8" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="24" t="inlineStr">
         <is>
@@ -8774,10 +8774,10 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="6.0" customHeight="true">
       <c r="A23" s="0"/>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="102.56" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="20" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
       <c r="T24" s="20"/>
       <c r="U24" s="20"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="91.8" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="91.8" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -8858,7 +8858,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="91.8" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -8881,7 +8881,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="91.8" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="26"/>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="U28" s="26"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="91.8" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="U29" s="28"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="91.8" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="23"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="U30" s="25"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="91.8" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="U31" s="25"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="91.8" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="26"/>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="U32" s="26"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="91.8" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -9039,7 +9039,7 @@
       <c r="T33" s="21"/>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="91.8" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="23"/>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="U34" s="23"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="91.8" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -9089,7 +9089,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="91.8" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="26"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="U36" s="27"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="91.8" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21"/>
       <c r="C37" s="22"/>
@@ -9139,7 +9139,7 @@
       <c r="T37" s="21"/>
       <c r="U37" s="22"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="91.8" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21"/>
       <c r="C38" s="23"/>
@@ -9162,7 +9162,7 @@
       <c r="T38" s="21"/>
       <c r="U38" s="23"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="91.8" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="23"/>
@@ -9185,7 +9185,7 @@
       <c r="T39" s="21"/>
       <c r="U39" s="23"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="91.8" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21"/>
       <c r="C40" s="26"/>
@@ -9208,7 +9208,7 @@
       <c r="T40" s="21"/>
       <c r="U40" s="26"/>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="91.8" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21"/>
       <c r="C41" s="22"/>
@@ -9231,7 +9231,7 @@
       <c r="T41" s="21"/>
       <c r="U41" s="22"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="91.8" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="23"/>
@@ -9254,7 +9254,7 @@
       <c r="T42" s="21"/>
       <c r="U42" s="23"/>
     </row>
-    <row r="43" ht="56" customHeight="1">
+    <row r="43" ht="91.8" customHeight="true">
       <c r="A43" s="0"/>
       <c r="B43" s="21"/>
       <c r="C43" s="23"/>
@@ -9277,7 +9277,7 @@
       <c r="T43" s="21"/>
       <c r="U43" s="23"/>
     </row>
-    <row r="44" ht="56" customHeight="1">
+    <row r="44" ht="91.8" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="21"/>
       <c r="C44" s="26"/>
@@ -9307,7 +9307,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="22" max="16383" man="1"/>
   </rowBreaks>
